--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484185_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484185_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4568</v>
+        <v>6.1709</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4018</v>
+        <v>2.2001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0549</v>
+        <v>3.9708</v>
       </c>
       <c r="G2" t="n">
         <v>1.1346</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5286</v>
+        <v>1.2428</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1541</v>
+        <v>0.9524</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3746</v>
+        <v>0.2904</v>
       </c>
       <c r="V2" t="n">
         <v>1.8097</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6427</v>
+        <v>4.6043</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.699</v>
+        <v>-1.7647</v>
       </c>
       <c r="F3" t="n">
-        <v>5.3417</v>
+        <v>6.369</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1799</v>
+        <v>0.9492</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4831</v>
+        <v>0.8016</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3032</v>
+        <v>0.1476</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.6974</v>
+        <v>-0.7749</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1779</v>
+        <v>-0.0998</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5195</v>
+        <v>-0.6751</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5176</v>
+        <v>1.7241</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6949</v>
+        <v>0.9014</v>
       </c>
       <c r="O3" t="n">
         <v>0.8227</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9758</v>
+        <v>3.7693</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7668</v>
+        <v>0.3259</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9184</v>
+        <v>0.1248</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8484</v>
+        <v>0.2011</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0639</v>
+        <v>1.5437</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0639</v>
+        <v>0.8692</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0337</v>
+        <v>3.3171</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8303</v>
+        <v>-1.716</v>
       </c>
       <c r="F4" t="n">
-        <v>5.864</v>
+        <v>5.0331</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9492</v>
+        <v>-0.1799</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8016</v>
+        <v>-0.4831</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1476</v>
+        <v>0.3032</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7749</v>
+        <v>-1.6974</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0998</v>
+        <v>-1.1779</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6751</v>
+        <v>-0.5195</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7241</v>
+        <v>1.5176</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9014</v>
+        <v>0.6949</v>
       </c>
       <c r="O4" t="n">
         <v>0.8227</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7693</v>
+        <v>2.9758</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2447</v>
+        <v>1.4411</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9408</v>
+        <v>0.9013</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3039</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5437</v>
+        <v>1.0639</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8692</v>
+        <v>1.0639</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4449</v>
+        <v>2.766</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7849</v>
+        <v>-1.6602</v>
       </c>
       <c r="F5" t="n">
-        <v>4.2298</v>
+        <v>4.4262</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9282</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7942</v>
+        <v>1.1152</v>
       </c>
       <c r="T5" t="n">
-        <v>0.856</v>
+        <v>0.9807</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0619</v>
+        <v>0.1345</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3072</v>
+        <v>2.4855</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.553</v>
+        <v>-3.1222</v>
       </c>
       <c r="F6" t="n">
-        <v>5.8602</v>
+        <v>5.6077</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1156</v>
@@ -922,13 +922,13 @@
         <v>3.1741</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4155</v>
+        <v>0.5938</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1982</v>
+        <v>0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6137</v>
+        <v>0.3612</v>
       </c>
       <c r="V6" t="n">
         <v>0.8171</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>M. COLL JANER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8781</v>
+        <v>1.594</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6102</v>
+        <v>0.4526</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2679</v>
+        <v>1.1414</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9769</v>
+        <v>-0.115</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.8825</v>
+        <v>-0.0658</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9056</v>
+        <v>-0.0492</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.99</v>
+        <v>0.1408</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.753</v>
+        <v>0.0605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7631</v>
+        <v>0.0803</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9869</v>
+        <v>-0.2558</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1295</v>
+        <v>-0.1263</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1425</v>
+        <v>-0.1295</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>4.0534</v>
+        <v>0.3203</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8456</v>
+        <v>0.3118</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2077</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. COLL JANER</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6888</v>
+        <v>0.5614</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2843</v>
+        <v>1.8355</v>
       </c>
       <c r="F8" t="n">
-        <v>0.973</v>
+        <v>-1.2742</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.115</v>
+        <v>0.5939</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0658</v>
+        <v>-1.497</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0492</v>
+        <v>2.091</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1408</v>
+        <v>2.1201</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0605</v>
+        <v>0.3077</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0803</v>
+        <v>1.8124</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2558</v>
+        <v>-1.5262</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1263</v>
+        <v>-1.8048</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1295</v>
+        <v>0.2786</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3887</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5849</v>
+        <v>0.3642</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4251</v>
+        <v>0.2268</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1599</v>
+        <v>0.1374</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0494</v>
+        <v>-0.2724</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3651</v>
+        <v>-1.1954</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4144</v>
+        <v>0.923</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5939</v>
+        <v>-1.5719</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.497</v>
+        <v>-0.2322</v>
       </c>
       <c r="I9" t="n">
-        <v>2.091</v>
+        <v>-1.3397</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1201</v>
+        <v>-0.385</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3077</v>
+        <v>0.9678</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8124</v>
+        <v>-1.3527</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5262</v>
+        <v>-1.1869</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8048</v>
+        <v>-1.1999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2786</v>
+        <v>0.013</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>1.5871</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2465</v>
+        <v>0.3869</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2436</v>
+        <v>-0.1359</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0029</v>
+        <v>0.5228</v>
       </c>
       <c r="V9" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.6745</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.4724</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-1.4724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5567</v>
+        <v>-0.7302</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5638</v>
+        <v>-1.857</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0071</v>
+        <v>1.1268</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5719</v>
+        <v>-0.5492</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2322</v>
+        <v>-0.2772</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3397</v>
+        <v>-0.2721</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.385</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9678</v>
+        <v>-0.0149</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3527</v>
+        <v>-0.6802</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1869</v>
+        <v>0.1458</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1999</v>
+        <v>-0.2623</v>
       </c>
       <c r="O10" t="n">
-        <v>0.013</v>
+        <v>0.4081</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5871</v>
+        <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2239</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.6032</v>
+      </c>
+      <c r="W10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.5871</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.1026</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.5044</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.6745</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.6745</v>
-      </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0029</v>
+        <v>-0.8871</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1857</v>
+        <v>-0.5097</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1829</v>
+        <v>-0.3774</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5492</v>
+        <v>-1.9769</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2772</v>
+        <v>-2.8825</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2721</v>
+        <v>0.9056</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.99</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0149</v>
+        <v>-1.753</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6802</v>
+        <v>0.7631</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1458</v>
+        <v>-0.9869</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2623</v>
+        <v>-1.1295</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4081</v>
+        <v>0.1425</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1984</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0488</v>
+        <v>1.2881</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4988</v>
+        <v>0.7257</v>
       </c>
       <c r="U11" t="n">
-        <v>0.45</v>
+        <v>0.5625</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6032</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3059</v>
+        <v>-2.2043</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4706</v>
+        <v>-2.7338</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1648</v>
+        <v>0.5295</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4811</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2135</v>
+        <v>-0.1119</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0485</v>
+        <v>-0.3117</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.165</v>
+        <v>0.1997</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6032</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6281</v>
+        <v>-3.9372</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1013</v>
+        <v>-5.4664</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4731</v>
+        <v>1.5292</v>
       </c>
       <c r="G13" t="n">
         <v>-5.7648</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5974</v>
+        <v>0.0936</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6744</v>
+        <v>-0.0396</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0771</v>
+        <v>0.1332</v>
       </c>
       <c r="V13" t="n">
         <v>0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.9092</v>
+        <v>13.468</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.0958</v>
+        <v>-15.5372</v>
       </c>
       <c r="F14" t="n">
-        <v>29.005</v>
+        <v>29.0051</v>
       </c>
       <c r="G14" t="n">
         <v>-11.0049</v>
@@ -1516,7 +1516,7 @@
         <v>-10.8098</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1949999999999994</v>
+        <v>-0.1950000000000003</v>
       </c>
       <c r="J14" t="n">
         <v>-11.9944</v>
@@ -1528,13 +1528,13 @@
         <v>-5.701500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9895000000000003</v>
+        <v>0.9895000000000007</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.5171</v>
+        <v>-4.517099999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>5.5065</v>
+        <v>5.506500000000001</v>
       </c>
       <c r="P14" t="n">
         <v>12.8949</v>
@@ -1546,13 +1546,13 @@
         <v>26.782</v>
       </c>
       <c r="S14" t="n">
-        <v>5.7253</v>
+        <v>7.283900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2403</v>
+        <v>3.7988</v>
       </c>
       <c r="U14" t="n">
-        <v>3.4849</v>
+        <v>3.485</v>
       </c>
       <c r="V14" t="n">
         <v>4.294</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.942</v>
+        <v>2.2985</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.1046</v>
+        <v>-0.1946</v>
       </c>
       <c r="F15" t="n">
-        <v>7.0466</v>
+        <v>2.4931</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3282</v>
+        <v>3.7397</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7254</v>
+        <v>3.4079</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6028</v>
+        <v>0.3317</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7102000000000001</v>
+        <v>1.8519</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7906</v>
+        <v>1.9673</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0803</v>
+        <v>-0.1154</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0384</v>
+        <v>1.8877</v>
       </c>
       <c r="N15" t="n">
-        <v>1.516</v>
+        <v>1.4406</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5224</v>
+        <v>0.4471</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1822</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.1661</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7322</v>
+        <v>-1.0444</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6177</v>
+        <v>-0.3286</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3499</v>
+        <v>-0.7158</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0639</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3894</v>
+        <v>0.266</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4152</v>
+        <v>1.3486</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2966</v>
+        <v>-5.1046</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7118</v>
+        <v>6.4532</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7397</v>
+        <v>2.3282</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4079</v>
+        <v>0.7254</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3317</v>
+        <v>1.6028</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8519</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9673</v>
+        <v>-0.7906</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1154</v>
+        <v>0.0803</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8877</v>
+        <v>3.0384</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4406</v>
+        <v>1.516</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4471</v>
+        <v>1.5224</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3968</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-4.1661</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9277</v>
+        <v>0.1388</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4307</v>
+        <v>-0.6177</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4971</v>
+        <v>0.7565</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0639</v>
       </c>
       <c r="W16" t="n">
-        <v>0.266</v>
+        <v>0.3894</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2499</v>
+        <v>1.1014</v>
       </c>
       <c r="E17" t="n">
-        <v>0.467</v>
+        <v>-0.855</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7829</v>
+        <v>1.9564</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7262</v>
+        <v>2.151</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9451</v>
+        <v>2.3634</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2189</v>
+        <v>-0.2124</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0281</v>
+        <v>0.0762</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9879</v>
+        <v>1.3964</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>-1.3202</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6981000000000001</v>
+        <v>2.0747</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9669</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2591</v>
+        <v>1.1078</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7935</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1903</v>
+        <v>-2.9758</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3968</v>
+        <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-1.0062</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6292</v>
+        <v>-0.3684</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7205</v>
+        <v>-0.6378</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4085</v>
+        <v>1.5437</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4085</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1643</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1611</v>
+        <v>0.0589</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3254</v>
+        <v>0.8671</v>
       </c>
       <c r="G18" t="n">
-        <v>2.151</v>
+        <v>1.7262</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3634</v>
+        <v>1.9451</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2124</v>
+        <v>-0.2189</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0762</v>
+        <v>1.0281</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3964</v>
+        <v>0.9879</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3202</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0747</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9669</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1078</v>
+        <v>-0.2591</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5871</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-1.1903</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9433</v>
+        <v>-0.4152</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6744</v>
+        <v>0.2211</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2689</v>
+        <v>-0.6363</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5437</v>
+        <v>0.4085</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8692</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5273</v>
+        <v>0.7619</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-1.0289</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4542</v>
+        <v>1.7909</v>
       </c>
       <c r="G19" t="n">
         <v>4.3341</v>
@@ -1936,13 +1936,13 @@
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9376</v>
+        <v>-0.7029</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1813</v>
+        <v>-0.2833</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7563</v>
+        <v>-0.4196</v>
       </c>
       <c r="V19" t="n">
         <v>-2.0757</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9583</v>
+        <v>-2.0527</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.2964</v>
+        <v>-6.1943</v>
       </c>
       <c r="F20" t="n">
-        <v>4.3381</v>
+        <v>4.1417</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2345</v>
@@ -2014,13 +2014,13 @@
         <v>2.1822</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3351</v>
+        <v>-0.4294</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0031</v>
+        <v>-0.9011</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6681</v>
+        <v>0.4717</v>
       </c>
       <c r="V20" t="n">
         <v>0.6032</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7397</v>
+        <v>-2.8698</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5951</v>
+        <v>0.4931</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3348</v>
+        <v>-3.3629</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1352</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3304</v>
+        <v>-0.4605</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0056</v>
+        <v>-0.1076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3248</v>
+        <v>-0.3529</v>
       </c>
       <c r="V21" t="n">
         <v>-2.0757</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6121</v>
+        <v>-3.1394</v>
       </c>
       <c r="E22" t="n">
         <v>-4.5525</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9404</v>
+        <v>1.4131</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4511</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9545</v>
+        <v>-0.4818</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3173</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6372</v>
+        <v>-0.1645</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8097</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5053</v>
+        <v>-4.3973</v>
       </c>
       <c r="E23" t="n">
         <v>-4.8284</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3231</v>
+        <v>0.4311</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9302</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1926</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.4096</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6745</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3925</v>
+        <v>-5.2063</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.9007</v>
+        <v>-6.7986</v>
       </c>
       <c r="F24" t="n">
-        <v>1.5081</v>
+        <v>1.5923</v>
       </c>
       <c r="G24" t="n">
         <v>0.477</v>
@@ -2326,13 +2326,13 @@
         <v>1.7855</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2273</v>
+        <v>-0.0411</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6914</v>
+        <v>-0.5894</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4641</v>
+        <v>0.5482</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2777</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.9092</v>
+        <v>-11.2292</v>
       </c>
       <c r="E25" t="n">
-        <v>-29.0051</v>
+        <v>-29.0049</v>
       </c>
       <c r="F25" t="n">
-        <v>17.0958</v>
+        <v>17.776</v>
       </c>
       <c r="G25" t="n">
         <v>11.0052</v>
@@ -2404,13 +2404,13 @@
         <v>13.8869</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.7252</v>
+        <v>-5.045</v>
       </c>
       <c r="T25" t="n">
         <v>-3.484900000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.2403</v>
+        <v>-1.5601</v>
       </c>
       <c r="V25" t="n">
         <v>-4.294</v>
